--- a/高经济价值第六期_加盟商准入续约/加盟商准入续约_v1_标准答案.xlsx
+++ b/高经济价值第六期_加盟商准入续约/加盟商准入续约_v1_标准答案.xlsx
@@ -855,7 +855,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>5个新加盟商申请中3家直接准入（J01。、J02。、J05）、2家整改后准入（J04。、J03）、0家拒绝；8家现有门店评级A级2家、B级2家、C级2家、D级2家；授权费按城市与商圈系数差异化收取，公司年度供应链毛利合计100.5万元、管理费合计56.1万元。</t>
+          <t>5个新加盟商申请中3家直接准入（J01、J02、J05）、2家整改后准入（J04、J03）、0家拒绝；8家现有门店评级A级2家、B级2家、C级2家、D级2家；授权费按城市与商圈系数差异化收取，公司年度供应链毛利合计100.5万元、管理费合计56.1万元。</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>新加盟商准入3家（J01。、J02。、J05）、整改后准入2家（J04。、J03）、拒绝0家（），按资金实力25%、选址评分30%、运营经验25%、历史合规20%加权评分。</t>
+          <t>新加盟商准入3家（J01、J02、J05）、整改后准入2家（J04、J03）、拒绝0家（），按资金实力25%、选址评分30%、运营经验25%、历史合规20%加权评分。</t>
         </is>
       </c>
     </row>

--- a/高经济价值第六期_加盟商准入续约/加盟商准入续约_v1_标准答案.xlsx
+++ b/高经济价值第六期_加盟商准入续约/加盟商准入续约_v1_标准答案.xlsx
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>准入只看资金实力，忽略选址和合规</t>
+          <t>这个加盟商资金实力很强，选址和合规差点也没关系，先放进来</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>四维度加权评分缺一不可</t>
+          <t>准入须四维度加权评分，缺一不可</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>有违规记录的加盟商直接拒绝，不考虑整改</t>
+          <t>只要有违规记录就直接拒，不用给整改机会</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>续约评级只看营收达成，忽略食安和客诉</t>
+          <t>续约就看营收达没达标，食安客诉不用看</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>须四项标准同时满足</t>
+          <t>续约评级须四项标准同时满足，就低判定</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>授权费按固定价收取，不看城市和商圈</t>
+          <t>授权费统一按500元/㎡收，别搞什么城市商圈系数</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>须按城市系数和商圈系数调整</t>
+          <t>授权费须按城市系数和商圈系数调整</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>保证金可以充抵货款</t>
+          <t>保证金先用来抵货款，后面再补</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D级门店直接收回，不给整改期</t>
+          <t>D级门店马上收回，别给整改期</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D级是合同到期后不续约，收回需按合同执行</t>
+          <t>D级是合同到期后不续约，收回须按合同执行</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>供应链毛利按门店营业额计提</t>
+          <t>公司从加盟店赚的钱按营业额提成就行</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>应按门店食材采购额计算</t>
+          <t>供应链毛利应按门店食材采购额计算</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>客诉率按投诉次数直接算，不按订单数</t>
+          <t>客诉率直接数投诉次数，不用除以订单量</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>须除以年度订单数</t>
+          <t>客诉率须采用订单数口径</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>巡店评分可由加盟商自评</t>
+          <t>巡店评分让加盟商自己填一下</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>须由公司巡店人员评定</t>
+          <t>巡店评分须由公司巡店人员评定</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>合同到期前无需提前通知续约</t>
+          <t>合同到期再说续约的事，不用提前通知</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>新加盟商可以免保证金</t>
+          <t>新加盟商是自己人，保证金免了</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>保证金为强制条款</t>
+          <t>保证金为强制条款，不得免除</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>加盟门店亏损由公司补贴</t>
+          <t>加盟店亏损公司补一下，别让加盟商跑了</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
